--- a/Gantt/Gantt_CIR2_2026.xlsx
+++ b/Gantt/Gantt_CIR2_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raf\Documents\Claude\Projects\Projet_fin_d'année_CIR2_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\ProjetFinal\projet-cir2-43\Gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9E4154-C501-44EF-8E64-97E0F2C06A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE68F5C-D0F6-4EFF-9936-6407327567F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt CIR2" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
   <si>
     <t>DIAGRAMME DE GANTT – Projet CIR2 2026 – Application IRVE Bretagne</t>
   </si>
@@ -108,9 +108,6 @@
     <t>Serveur</t>
   </si>
   <si>
-    <t>Vérif. enseignants mercredi</t>
-  </si>
-  <si>
     <t>Création BDD &amp; import données CSV</t>
   </si>
   <si>
@@ -135,21 +132,12 @@
     <t>API</t>
   </si>
   <si>
-    <t>Tests &amp; intégration continue</t>
-  </si>
-  <si>
     <t>Tests</t>
   </si>
   <si>
-    <t>Recette fonctionnelle finale</t>
-  </si>
-  <si>
     <t>Recette</t>
   </si>
   <si>
-    <t>Lundi S2 + mardi matin</t>
-  </si>
-  <si>
     <t>⚠ LIVRABLE: Dépôt rendu final</t>
   </si>
   <si>
@@ -175,6 +163,9 @@
   </si>
   <si>
     <t>9h</t>
+  </si>
+  <si>
+    <t>Documentation</t>
   </si>
 </sst>
 </file>
@@ -249,7 +240,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,6 +383,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC0392B"/>
         <bgColor rgb="FFE74C3C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFCA6F1E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFE74C3C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFE67E22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF16A085"/>
       </patternFill>
     </fill>
   </fills>
@@ -422,20 +437,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -515,9 +518,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -530,6 +530,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -795,7 +814,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -803,379 +822,375 @@
     <col min="4" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+    </row>
+    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="1" t="s">
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="5" t="s">
+      <c r="J2" s="41"/>
+    </row>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="7" t="s">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-    </row>
-    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="19" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="21" t="s">
+      <c r="D9" s="9"/>
+      <c r="E9" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-    </row>
-    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="23" t="s">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="B11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="C11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="B12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-    </row>
-    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="13"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="33" t="s">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+    </row>
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13"/>
+      <c r="B21" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="F21" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="28"/>
+      <c r="H21" s="35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="31"/>
+      <c r="B22" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="32"/>
+      <c r="D22" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17"/>
-      <c r="B21" s="40" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="40" t="s">
+      <c r="G22" s="37"/>
+      <c r="H22" s="35" t="s">
         <v>44</v>
-      </c>
-      <c r="G21" s="32"/>
-      <c r="H21" s="40" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="35"/>
-      <c r="B22" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="41"/>
-      <c r="F22" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="42"/>
-      <c r="H22" s="40" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1189,6 +1204,6 @@
     <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>